--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Seymour_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Seymour_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{5F741EB4-9B88-E34F-9972-0A7EC792996A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA0F82CB-902E-4345-AD0C-AF0BAD2420D8}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -774,7 +774,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -819,12 +819,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C18" s="4">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C32" s="4">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C33" s="4">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="E3" s="8">
         <f>'MFSP CO2 Corrected'!B8</f>
-        <v>6.4089302995405149</v>
+        <v>6.6509708850468314</v>
       </c>
       <c r="F3" s="8">
         <f>'MFSP WACC Corrected'!B8</f>
-        <v>6.4810746306253213</v>
+        <v>6.719635538021123</v>
       </c>
       <c r="G3" s="10">
         <f>'FLH Sensitivity Parameters'!B12</f>
-        <v>9.848496505529857</v>
+        <v>10.106282178471034</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>131</v>
@@ -1678,11 +1678,11 @@
       </c>
       <c r="M3" s="8">
         <f>'MFSP CO2 Corrected'!B17</f>
-        <v>1.995010348012441</v>
+        <v>2.1119513050548209</v>
       </c>
       <c r="N3" s="8">
         <f>'MFSP WACC Corrected'!B17</f>
-        <v>2.0270625378636451</v>
+        <v>2.1423223021110553</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1702,15 +1702,15 @@
       </c>
       <c r="E4" s="8">
         <f>E3/Inputs!$C$6</f>
-        <v>7.1210336661561273</v>
+        <v>7.3899676500520348</v>
       </c>
       <c r="F4" s="8">
         <f>F3/Inputs!$C$6</f>
-        <v>7.2011940340281342</v>
+        <v>7.4662617089123584</v>
       </c>
       <c r="G4" s="10">
         <f>G3/Inputs!$C$6</f>
-        <v>10.942773895033174</v>
+        <v>11.22920242052337</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>131</v>
@@ -1728,11 +1728,11 @@
       </c>
       <c r="M4" s="8">
         <f>M3/Inputs!$C$6</f>
-        <v>2.2166781644582678</v>
+        <v>2.346612561172023</v>
       </c>
       <c r="N4" s="8">
         <f>N3/Inputs!$C$6</f>
-        <v>2.2522917087373835</v>
+        <v>2.3803581134567282</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="K5" s="12">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L5" s="12">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M5" s="12">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="N5" s="12">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2002,15 +2002,15 @@
       </c>
       <c r="E10" s="14">
         <f>((E4-E5) /E9 )* 10^6</f>
-        <v>2280.457070487606</v>
+        <v>2377.4811392492534</v>
       </c>
       <c r="F10" s="14">
         <f>((F4-F5) /F9 )* 10^6</f>
-        <v>2309.3767515621366</v>
+        <v>2405.0059611618103</v>
       </c>
       <c r="G10" s="18">
         <f>((G4-G5) /G9 )* 10^6</f>
-        <v>3659.2370275020467</v>
+        <v>3762.5726511739686</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>139</v>
@@ -2020,19 +2020,19 @@
       </c>
       <c r="K10" s="14">
         <f>((K4-K5) /K9 )* 10^6</f>
-        <v>431.97379407874388</v>
+        <v>107.27826612612451</v>
       </c>
       <c r="L10" s="14">
         <f>((L4-L5) /L9 )* 10^6</f>
-        <v>204.76453827624579</v>
+        <v>-119.9309896763736</v>
       </c>
       <c r="M10" s="14">
         <f>((M4-M5) /M9 )* 10^6</f>
-        <v>511.09896060858341</v>
+        <v>233.28022992282828</v>
       </c>
       <c r="N10" s="14">
         <f>((N4-N5) /N9 )* 10^6</f>
-        <v>523.94735901077388</v>
+        <v>245.4547076063117</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C15" s="20">
         <f>C14*10^-6*Inputs!$C$32</f>
-        <v>0.39118948000000003</v>
+        <v>0.41834694000000006</v>
       </c>
       <c r="I15" s="19" t="s">
         <v>142</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="K15" s="20">
         <f>K14*10^-6*Inputs!$C$33</f>
-        <v>0.14646720000000002</v>
+        <v>0.15958822</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C16" s="20">
         <f>F4+C15</f>
-        <v>7.5923835140281346</v>
+        <v>7.8846086489123586</v>
       </c>
       <c r="I16" s="19" t="s">
         <v>143</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="K16" s="20">
         <f>N4+K15</f>
-        <v>2.3987589087373835</v>
+        <v>2.539946333456728</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C17" s="4">
         <f>(C16-C5) /C9 * 10^6</f>
-        <v>2450.5072790489262</v>
+        <v>2555.9341617736582</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>144</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="K17" s="4">
         <f>(K16-K5) /K9 * 10^6</f>
-        <v>576.78874215715382</v>
+        <v>303.02979799288806</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B28" s="12">
         <f>(Inputs!C32*'Study Parameters'!C20)/10^6</f>
-        <v>7.861224</v>
+        <v>8.4069719999999997</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>91</v>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="H28" s="12">
         <f>(Inputs!C33*'Study Parameters'!C20) / 10^6</f>
-        <v>2.9433600000000002</v>
+        <v>3.207036</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>91</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B29" s="23">
         <f>B27-B19+B28</f>
-        <v>12.552470875000001</v>
+        <v>13.098218875000001</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>91</v>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H29" s="23">
         <f>H27-H19+H28</f>
-        <v>3.8353225000000002</v>
+        <v>4.0989985000000004</v>
       </c>
       <c r="I29" s="22" t="s">
         <v>91</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B36" s="8">
         <f>B28*4200/8760</f>
-        <v>3.7690800000000002</v>
+        <v>4.0307399999999998</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>91</v>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B37" s="8">
         <f>B27-B19+B36</f>
-        <v>8.4603268750000016</v>
+        <v>8.7219868750000025</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>91</v>
@@ -6436,123 +6436,123 @@
       </c>
       <c r="C3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="D3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="E3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="F3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="G3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="H3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="I3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="J3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="K3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="L3" s="4">
         <f>'Cost Components'!$B$29 * 10^6 + 'Cost Components'!B10 * 10^6</f>
-        <v>16845110.875</v>
+        <v>17390858.875</v>
       </c>
       <c r="M3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="N3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="O3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="P3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="Q3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="R3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="S3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="T3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="U3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="V3">
         <f>'Cost Components'!$B$29 * 10^6 + 'Cost Components'!B10 * 10^6</f>
-        <v>16845110.875</v>
+        <v>17390858.875</v>
       </c>
       <c r="W3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="X3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="Y3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="Z3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AA3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AB3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AC3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AD3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AE3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AF3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -6565,123 +6565,123 @@
       </c>
       <c r="C4">
         <f>C3 / (1+'Study Parameters'!$C$3) ^C2</f>
-        <v>11954734.166666666</v>
+        <v>12474494.166666666</v>
       </c>
       <c r="D4">
         <f>D3 / (1+'Study Parameters'!$C$3) ^D2</f>
-        <v>11385461.11111111</v>
+        <v>11880470.634920634</v>
       </c>
       <c r="E4">
         <f>E3 / (1+'Study Parameters'!$C$3) ^E2</f>
-        <v>10843296.296296295</v>
+        <v>11314733.938019652</v>
       </c>
       <c r="F4">
         <f>F3 / (1+'Study Parameters'!$C$3) ^F2</f>
-        <v>10326948.853615521</v>
+        <v>10775937.083828241</v>
       </c>
       <c r="G4">
         <f>G3 / (1+'Study Parameters'!$C$3) ^G2</f>
-        <v>9835189.3843957335</v>
+        <v>10262797.222693561</v>
       </c>
       <c r="H4">
         <f>H3 / (1+'Study Parameters'!$C$3) ^H2</f>
-        <v>9366847.0327578411</v>
+        <v>9774092.5930414889</v>
       </c>
       <c r="I4">
         <f>I3 / (1+'Study Parameters'!$C$3) ^I2</f>
-        <v>8920806.6978646088</v>
+        <v>9308659.6124204621</v>
       </c>
       <c r="J4">
         <f>J3 / (1+'Study Parameters'!$C$3) ^J2</f>
-        <v>8496006.3789186776</v>
+        <v>8865390.1070671082</v>
       </c>
       <c r="K4">
         <f>K3 / (1+'Study Parameters'!$C$3) ^K2</f>
-        <v>8091434.6465892158</v>
+        <v>8443228.6733972467</v>
       </c>
       <c r="L4">
         <f>L3 / (1+'Study Parameters'!$C$3) ^L2</f>
-        <v>10341436.823526077</v>
+        <v>10676478.75381944</v>
       </c>
       <c r="M4">
         <f>M3 / (1+'Study Parameters'!$C$3) ^M2</f>
-        <v>7339169.747473211</v>
+        <v>7658257.3001335561</v>
       </c>
       <c r="N4">
         <f>N3 / (1+'Study Parameters'!$C$3) ^N2</f>
-        <v>6989685.4737840118</v>
+        <v>7293578.3810795778</v>
       </c>
       <c r="O4">
         <f>O3 / (1+'Study Parameters'!$C$3) ^O2</f>
-        <v>6656843.308365724</v>
+        <v>6946265.1248376919</v>
       </c>
       <c r="P4">
         <f>P3 / (1+'Study Parameters'!$C$3) ^P2</f>
-        <v>6339850.7698721197</v>
+        <v>6615490.595083518</v>
       </c>
       <c r="Q4">
         <f>Q3 / (1+'Study Parameters'!$C$3) ^Q2</f>
-        <v>6037953.1141639212</v>
+        <v>6300467.2334128721</v>
       </c>
       <c r="R4">
         <f>R3 / (1+'Study Parameters'!$C$3) ^R2</f>
-        <v>5750431.5372989736</v>
+        <v>6000444.9842027361</v>
       </c>
       <c r="S4">
         <f>S3 / (1+'Study Parameters'!$C$3) ^S2</f>
-        <v>5476601.4640942598</v>
+        <v>5714709.50876451</v>
       </c>
       <c r="T4">
         <f>T3 / (1+'Study Parameters'!$C$3) ^T2</f>
-        <v>5215810.9181850096</v>
+        <v>5442580.4845376285</v>
       </c>
       <c r="U4">
         <f>U3 / (1+'Study Parameters'!$C$3) ^U2</f>
-        <v>4967438.9697000086</v>
+        <v>5183409.9852739321</v>
       </c>
       <c r="V4">
         <f>V3 / (1+'Study Parameters'!$C$3) ^V2</f>
-        <v>6348745.1266171085</v>
+        <v>6554431.808116083</v>
       </c>
       <c r="W4">
         <f>W3 / (1+'Study Parameters'!$C$3) ^W2</f>
-        <v>4505613.577959192</v>
+        <v>4701505.6555772629</v>
       </c>
       <c r="X4">
         <f>X3 / (1+'Study Parameters'!$C$3) ^X2</f>
-        <v>4291060.5504373256</v>
+        <v>4477624.4338831073</v>
       </c>
       <c r="Y4">
         <f>Y3 / (1+'Study Parameters'!$C$3) ^Y2</f>
-        <v>4086724.3337498335</v>
+        <v>4264404.2227458162</v>
       </c>
       <c r="Z4">
         <f>Z3 / (1+'Study Parameters'!$C$3) ^Z2</f>
-        <v>3892118.4130950798</v>
+        <v>4061337.3549960158</v>
       </c>
       <c r="AA4">
         <f>AA3 / (1+'Study Parameters'!$C$3) ^AA2</f>
-        <v>3706779.4410429331</v>
+        <v>3867940.3380914433</v>
       </c>
       <c r="AB4">
         <f>AB3 / (1+'Study Parameters'!$C$3) ^AB2</f>
-        <v>3530266.1343266028</v>
+        <v>3683752.7029442317</v>
       </c>
       <c r="AC4">
         <f>AC3 / (1+'Study Parameters'!$C$3) ^AC2</f>
-        <v>3362158.2231681929</v>
+        <v>3508335.9075659346</v>
       </c>
       <c r="AD4">
         <f>AD3 / (1+'Study Parameters'!$C$3) ^AD2</f>
-        <v>3202055.4506363748</v>
+        <v>3341272.292919938</v>
       </c>
       <c r="AE4">
         <f>AE3 / (1+'Study Parameters'!$C$3) ^AE2</f>
-        <v>3049576.6196536897</v>
+        <v>3182164.0884951786</v>
       </c>
       <c r="AF4">
         <f>AF3 / (1+'Study Parameters'!$C$3) ^AF2</f>
-        <v>2904358.6853844672</v>
+        <v>3030632.4652335043</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B8">
         <f>SUM(B4:AF4) /SUM(B6:AF6)</f>
-        <v>6.4089302995405149</v>
+        <v>6.6509708850468314</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -7064,123 +7064,123 @@
       </c>
       <c r="C12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="D12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="E12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="F12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="G12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="H12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="I12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="J12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="K12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="L12">
         <f>'Cost Components'!$H$29 * 10^6 + 'Cost Components'!H10 * 10^6</f>
-        <v>4909322.5</v>
+        <v>5172998.5</v>
       </c>
       <c r="M12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="N12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="O12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="P12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="Q12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="R12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="S12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="T12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="U12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="V12">
         <f>'Cost Components'!$H$29 * 10^6+ 'Cost Components'!H10 * 10^6</f>
-        <v>4909322.5</v>
+        <v>5172998.5</v>
       </c>
       <c r="W12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="X12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="Y12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="Z12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AA12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AB12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AC12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AD12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AE12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AF12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -7193,123 +7193,123 @@
       </c>
       <c r="C13">
         <f>C12 / (1+'Study Parameters'!$C$3) ^C11</f>
-        <v>3652688.0952380951</v>
+        <v>3903808.0952380956</v>
       </c>
       <c r="D13">
         <f>D12 / (1+'Study Parameters'!$C$3) ^D11</f>
-        <v>3478750.5668934239</v>
+        <v>3717912.4716553292</v>
       </c>
       <c r="E13">
         <f>E12 / (1+'Study Parameters'!$C$3) ^E11</f>
-        <v>3313095.7779937368</v>
+        <v>3540869.0206241226</v>
       </c>
       <c r="F13">
         <f>F12 / (1+'Study Parameters'!$C$3) ^F11</f>
-        <v>3155329.3123749876</v>
+        <v>3372256.2101182123</v>
       </c>
       <c r="G13">
         <f>G12 / (1+'Study Parameters'!$C$3) ^G11</f>
-        <v>3005075.5355952261</v>
+        <v>3211672.5810649637</v>
       </c>
       <c r="H13">
         <f>H12 / (1+'Study Parameters'!$C$3) ^H11</f>
-        <v>2861976.7005668823</v>
+        <v>3058735.7914904421</v>
       </c>
       <c r="I13">
         <f>I12 / (1+'Study Parameters'!$C$3) ^I11</f>
-        <v>2725692.0957779828</v>
+        <v>2913081.706181373</v>
       </c>
       <c r="J13">
         <f>J12 / (1+'Study Parameters'!$C$3) ^J11</f>
-        <v>2595897.2340742694</v>
+        <v>2774363.529696546</v>
       </c>
       <c r="K13">
         <f>K12 / (1+'Study Parameters'!$C$3) ^K11</f>
-        <v>2472283.0800707326</v>
+        <v>2642250.9806633769</v>
       </c>
       <c r="L13">
         <f>L12 / (1+'Study Parameters'!$C$3) ^L11</f>
-        <v>3013898.1486558542</v>
+        <v>3175772.3396964674</v>
       </c>
       <c r="M13">
         <f>M12 / (1+'Study Parameters'!$C$3) ^M11</f>
-        <v>2242433.6327172178</v>
+        <v>2396599.5289463736</v>
       </c>
       <c r="N13">
         <f>N12 / (1+'Study Parameters'!$C$3) ^N11</f>
-        <v>2135651.0787783028</v>
+        <v>2282475.7418536893</v>
       </c>
       <c r="O13">
         <f>O12 / (1+'Study Parameters'!$C$3) ^O11</f>
-        <v>2033953.4083602882</v>
+        <v>2173786.4208130371</v>
       </c>
       <c r="P13">
         <f>P12 / (1+'Study Parameters'!$C$3) ^P11</f>
-        <v>1937098.4841526558</v>
+        <v>2070272.7817267026</v>
       </c>
       <c r="Q13">
         <f>Q12 / (1+'Study Parameters'!$C$3) ^Q11</f>
-        <v>1844855.699193005</v>
+        <v>1971688.3635492399</v>
       </c>
       <c r="R13">
         <f>R12 / (1+'Study Parameters'!$C$3) ^R11</f>
-        <v>1757005.4278028621</v>
+        <v>1877798.4414754668</v>
       </c>
       <c r="S13">
         <f>S12 / (1+'Study Parameters'!$C$3) ^S11</f>
-        <v>1673338.5026693922</v>
+        <v>1788379.4680718728</v>
       </c>
       <c r="T13">
         <f>T12 / (1+'Study Parameters'!$C$3) ^T11</f>
-        <v>1593655.7168279926</v>
+        <v>1703218.5410208313</v>
       </c>
       <c r="U13">
         <f>U12 / (1+'Study Parameters'!$C$3) ^U11</f>
-        <v>1517767.3493599929</v>
+        <v>1622112.8962103154</v>
       </c>
       <c r="V13">
         <f>V12 / (1+'Study Parameters'!$C$3) ^V11</f>
-        <v>1850272.0182817865</v>
+        <v>1949648.7295678079</v>
       </c>
       <c r="W13">
         <f>W12 / (1+'Study Parameters'!$C$3) ^W11</f>
-        <v>1376659.7273106512</v>
+        <v>1471304.2142497194</v>
       </c>
       <c r="X13">
         <f>X12 / (1+'Study Parameters'!$C$3) ^X11</f>
-        <v>1311104.5022006205</v>
+        <v>1401242.1088092567</v>
       </c>
       <c r="Y13">
         <f>Y12 / (1+'Study Parameters'!$C$3) ^Y11</f>
-        <v>1248670.954476781</v>
+        <v>1334516.2941040536</v>
       </c>
       <c r="Z13">
         <f>Z12 / (1+'Study Parameters'!$C$3) ^Z11</f>
-        <v>1189210.4328350297</v>
+        <v>1270967.899146718</v>
       </c>
       <c r="AA13">
         <f>AA12 / (1+'Study Parameters'!$C$3) ^AA11</f>
-        <v>1132581.3646047902</v>
+        <v>1210445.6182349694</v>
       </c>
       <c r="AB13">
         <f>AB12 / (1+'Study Parameters'!$C$3) ^AB11</f>
-        <v>1078648.9186712287</v>
+        <v>1152805.350699971</v>
       </c>
       <c r="AC13">
         <f>AC12 / (1+'Study Parameters'!$C$3) ^AC11</f>
-        <v>1027284.6844487891</v>
+        <v>1097909.8578094959</v>
       </c>
       <c r="AD13">
         <f>AD12 / (1+'Study Parameters'!$C$3) ^AD11</f>
-        <v>978366.36614170414</v>
+        <v>1045628.4360090439</v>
       </c>
       <c r="AE13">
         <f>AE12 / (1+'Study Parameters'!$C$3) ^AE11</f>
-        <v>931777.4915635275</v>
+        <v>995836.60572289873</v>
       </c>
       <c r="AF13">
         <f>AF12 / (1+'Study Parameters'!$C$3) ^AF11</f>
-        <v>887407.1348224075</v>
+        <v>948415.81497418962</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B17">
         <f>SUM(B13:AF13) /SUM(B15:AF15)</f>
-        <v>1.995010348012441</v>
+        <v>2.1119513050548209</v>
       </c>
     </row>
   </sheetData>
@@ -7706,123 +7706,123 @@
       </c>
       <c r="C3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="D3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="E3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="F3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="G3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="H3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="I3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="J3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="K3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="L3" s="4">
         <f>'Cost Components'!$B$29 * 10^6 + 'Cost Components'!B10 * 10^6</f>
-        <v>16845110.875</v>
+        <v>17390858.875</v>
       </c>
       <c r="M3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="N3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="O3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="P3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="Q3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="R3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="S3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="T3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="U3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="V3">
         <f>'Cost Components'!$B$29 * 10^6 + 'Cost Components'!B10 * 10^6</f>
-        <v>16845110.875</v>
+        <v>17390858.875</v>
       </c>
       <c r="W3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="X3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="Y3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="Z3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AA3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AB3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AC3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AD3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AE3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
       <c r="AF3" s="4">
         <f>'Cost Components'!$B$29 * 10^6</f>
-        <v>12552470.875</v>
+        <v>13098218.875</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -7835,123 +7835,123 @@
       </c>
       <c r="C4">
         <f>C3 / (1+'Cost Components'!$B$30) ^C2</f>
-        <v>11731281.191588784</v>
+        <v>12241326.051401868</v>
       </c>
       <c r="D4">
         <f>D3 / (1+'Cost Components'!$B$30) ^D2</f>
-        <v>10963814.197746528</v>
+        <v>11440491.636824176</v>
       </c>
       <c r="E4">
         <f>E3 / (1+'Cost Components'!$B$30) ^E2</f>
-        <v>10246555.324996755</v>
+        <v>10692048.258714182</v>
       </c>
       <c r="F4">
         <f>F3 / (1+'Cost Components'!$B$30) ^F2</f>
-        <v>9576219.9299035091</v>
+        <v>9992568.466088023</v>
       </c>
       <c r="G4">
         <f>G3 / (1+'Cost Components'!$B$30) ^G2</f>
-        <v>8949738.25224627</v>
+        <v>9338849.0337271225</v>
       </c>
       <c r="H4">
         <f>H3 / (1+'Cost Components'!$B$30) ^H2</f>
-        <v>8364241.3572395053</v>
+        <v>8727896.2932029199</v>
       </c>
       <c r="I4">
         <f>I3 / (1+'Cost Components'!$B$30) ^I2</f>
-        <v>7817047.9974200977</v>
+        <v>8156912.423554129</v>
       </c>
       <c r="J4">
         <f>J3 / (1+'Cost Components'!$B$30) ^J2</f>
-        <v>7305652.3340374744</v>
+        <v>7623282.638835635</v>
       </c>
       <c r="K4">
         <f>K3 / (1+'Cost Components'!$B$30) ^K2</f>
-        <v>6827712.4617172647</v>
+        <v>7124563.213865079</v>
       </c>
       <c r="L4">
         <f>L3 / (1+'Cost Components'!$B$30) ^L2</f>
-        <v>8563200.1892370861</v>
+        <v>8840630.7987210248</v>
       </c>
       <c r="M4">
         <f>M3 / (1+'Cost Components'!$B$30) ^M2</f>
-        <v>5963588.4895774871</v>
+        <v>6222869.4330204194</v>
       </c>
       <c r="N4">
         <f>N3 / (1+'Cost Components'!$B$30) ^N2</f>
-        <v>5573447.186521017</v>
+        <v>5815765.8252527295</v>
       </c>
       <c r="O4">
         <f>O3 / (1+'Cost Components'!$B$30) ^O2</f>
-        <v>5208829.1462813234</v>
+        <v>5435295.1637875969</v>
       </c>
       <c r="P4">
         <f>P3 / (1+'Cost Components'!$B$30) ^P2</f>
-        <v>4868064.6226928262</v>
+        <v>5079715.1063435487</v>
       </c>
       <c r="Q4">
         <f>Q3 / (1+'Cost Components'!$B$30) ^Q2</f>
-        <v>4549593.1053203978</v>
+        <v>4747397.2956481762</v>
       </c>
       <c r="R4">
         <f>R3 / (1+'Cost Components'!$B$30) ^R2</f>
-        <v>4251956.1731966343</v>
+        <v>4436819.9024749314</v>
       </c>
       <c r="S4">
         <f>S3 / (1+'Cost Components'!$B$30) ^S2</f>
-        <v>3973790.8160716207</v>
+        <v>4146560.6565186279</v>
       </c>
       <c r="T4">
         <f>T3 / (1+'Cost Components'!$B$30) ^T2</f>
-        <v>3713823.1925902995</v>
+        <v>3875290.333194979</v>
       </c>
       <c r="U4">
         <f>U3 / (1+'Cost Components'!$B$30) ^U2</f>
-        <v>3470862.7968133637</v>
+        <v>3621766.6665373635</v>
       </c>
       <c r="V4">
         <f>V3 / (1+'Cost Components'!$B$30) ^V2</f>
-        <v>4353096.7546065552</v>
+        <v>4494128.4085542187</v>
       </c>
       <c r="W4">
         <f>W3 / (1+'Cost Components'!$B$30) ^W2</f>
-        <v>3031585.9872594671</v>
+        <v>3163391.2713227035</v>
       </c>
       <c r="X4">
         <f>X3 / (1+'Cost Components'!$B$30) ^X2</f>
-        <v>2833257.9320181934</v>
+        <v>2956440.440488508</v>
       </c>
       <c r="Y4">
         <f>Y3 / (1+'Cost Components'!$B$30) ^Y2</f>
-        <v>2647904.6093627978</v>
+        <v>2763028.4490546803</v>
       </c>
       <c r="Z4">
         <f>Z3 / (1+'Cost Components'!$B$30) ^Z2</f>
-        <v>2474677.2050119601</v>
+        <v>2582269.5785557758</v>
       </c>
       <c r="AA4">
         <f>AA3 / (1+'Cost Components'!$B$30) ^AA2</f>
-        <v>2312782.4345906167</v>
+        <v>2413336.0547250244</v>
       </c>
       <c r="AB4">
         <f>AB3 / (1+'Cost Components'!$B$30) ^AB2</f>
-        <v>2161478.9108323525</v>
+        <v>2255454.2567523592</v>
       </c>
       <c r="AC4">
         <f>AC3 / (1+'Cost Components'!$B$30) ^AC2</f>
-        <v>2020073.7484414505</v>
+        <v>2107901.1745349145</v>
       </c>
       <c r="AD4">
         <f>AD3 / (1+'Cost Components'!$B$30) ^AD2</f>
-        <v>1887919.3910667766</v>
+        <v>1970001.0976961823</v>
       </c>
       <c r="AE4">
         <f>AE3 / (1+'Cost Components'!$B$30) ^AE2</f>
-        <v>1764410.6458568005</v>
+        <v>1841122.5212113853</v>
       </c>
       <c r="AF4">
         <f>AF3 / (1+'Cost Components'!$B$30) ^AF2</f>
-        <v>1648981.9120157014</v>
+        <v>1720675.2534685845</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="B8">
         <f>SUM(B4:AF4) /SUM(B6:AF6)</f>
-        <v>6.4810746306253213</v>
+        <v>6.719635538021123</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -8334,123 +8334,123 @@
       </c>
       <c r="C12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="D12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="E12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="F12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="G12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="H12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="I12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="J12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="K12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="L12">
         <f>'Cost Components'!$H$29 * 10^6 + 'Cost Components'!H10 * 10^6</f>
-        <v>4909322.5</v>
+        <v>5172998.5</v>
       </c>
       <c r="M12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="N12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="O12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="P12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="Q12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="R12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="S12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="T12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="U12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="V12">
         <f>'Cost Components'!$H$29 * 10^6+ 'Cost Components'!H10 * 10^6</f>
-        <v>4909322.5</v>
+        <v>5172998.5</v>
       </c>
       <c r="W12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="X12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="Y12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="Z12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AA12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AB12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AC12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AD12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AE12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
       <c r="AF12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>3835322.5</v>
+        <v>4098998.5000000005</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -8463,123 +8463,123 @@
       </c>
       <c r="C13">
         <f>C12 / (1+'Cost Components'!$B$30) ^C11</f>
-        <v>3584413.5514018689</v>
+        <v>3830839.7196261683</v>
       </c>
       <c r="D13">
         <f>D12 / (1+'Cost Components'!$B$30) ^D11</f>
-        <v>3349919.2069176347</v>
+        <v>3580224.0370338024</v>
       </c>
       <c r="E13">
         <f>E12 / (1+'Cost Components'!$B$30) ^E11</f>
-        <v>3130765.6139417146</v>
+        <v>3346003.7729287869</v>
       </c>
       <c r="F13">
         <f>F12 / (1+'Cost Components'!$B$30) ^F11</f>
-        <v>2925949.1719081444</v>
+        <v>3127106.3298399881</v>
       </c>
       <c r="G13">
         <f>G12 / (1+'Cost Components'!$B$30) ^G11</f>
-        <v>2734531.9363627518</v>
+        <v>2922529.2802242879</v>
       </c>
       <c r="H13">
         <f>H12 / (1+'Cost Components'!$B$30) ^H11</f>
-        <v>2555637.3237035065</v>
+        <v>2731335.7759105493</v>
       </c>
       <c r="I13">
         <f>I12 / (1+'Cost Components'!$B$30) ^I11</f>
-        <v>2388446.0969191645</v>
+        <v>2552650.2578603262</v>
       </c>
       <c r="J13">
         <f>J12 / (1+'Cost Components'!$B$30) ^J11</f>
-        <v>2232192.6139431447</v>
+        <v>2385654.4465984358</v>
       </c>
       <c r="K13">
         <f>K12 / (1+'Cost Components'!$B$30) ^K11</f>
-        <v>2086161.321442191</v>
+        <v>2229583.5949518089</v>
       </c>
       <c r="L13">
         <f>L12 / (1+'Cost Components'!$B$30) ^L11</f>
-        <v>2495650.6177360429</v>
+        <v>2629690.1256889571</v>
       </c>
       <c r="M13">
         <f>M12 / (1+'Cost Components'!$B$30) ^M11</f>
-        <v>1822134.0915732298</v>
+        <v>1947404.6597535233</v>
       </c>
       <c r="N13">
         <f>N12 / (1+'Cost Components'!$B$30) ^N11</f>
-        <v>1702929.057545075</v>
+        <v>1820004.3549098354</v>
       </c>
       <c r="O13">
         <f>O12 / (1+'Cost Components'!$B$30) ^O11</f>
-        <v>1591522.4836869859</v>
+        <v>1700938.6494484441</v>
       </c>
       <c r="P13">
         <f>P12 / (1+'Cost Components'!$B$30) ^P11</f>
-        <v>1487404.1903616691</v>
+        <v>1589662.2892041535</v>
       </c>
       <c r="Q13">
         <f>Q12 / (1+'Cost Components'!$B$30) ^Q11</f>
-        <v>1390097.3741697839</v>
+        <v>1485665.6908450029</v>
       </c>
       <c r="R13">
         <f>R12 / (1+'Cost Components'!$B$30) ^R11</f>
-        <v>1299156.4244577421</v>
+        <v>1388472.608266358</v>
       </c>
       <c r="S13">
         <f>S12 / (1+'Cost Components'!$B$30) ^S11</f>
-        <v>1214164.8826707872</v>
+        <v>1297637.951650802</v>
       </c>
       <c r="T13">
         <f>T12 / (1+'Cost Components'!$B$30) ^T11</f>
-        <v>1134733.535206343</v>
+        <v>1212745.7492063569</v>
       </c>
       <c r="U13">
         <f>U12 / (1+'Cost Components'!$B$30) ^U11</f>
-        <v>1060498.6310339654</v>
+        <v>1133407.2422489317</v>
       </c>
       <c r="V13">
         <f>V12 / (1+'Cost Components'!$B$30) ^V11</f>
-        <v>1268662.2249416888</v>
+        <v>1336801.1139276386</v>
       </c>
       <c r="W13">
         <f>W12 / (1+'Cost Components'!$B$30) ^W11</f>
-        <v>926280.57562578865</v>
+        <v>989961.78028555482</v>
       </c>
       <c r="X13">
         <f>X12 / (1+'Cost Components'!$B$30) ^X11</f>
-        <v>865682.78095868102</v>
+        <v>925197.92550051853</v>
       </c>
       <c r="Y13">
         <f>Y12 / (1+'Cost Components'!$B$30) ^Y11</f>
-        <v>809049.32799876726</v>
+        <v>864670.95841169951</v>
       </c>
       <c r="Z13">
         <f>Z12 / (1+'Cost Components'!$B$30) ^Z11</f>
-        <v>756120.86728856748</v>
+        <v>808103.69945018645</v>
       </c>
       <c r="AA13">
         <f>AA12 / (1+'Cost Components'!$B$30) ^AA11</f>
-        <v>706655.01615753968</v>
+        <v>755237.10228989378</v>
       </c>
       <c r="AB13">
         <f>AB12 / (1+'Cost Components'!$B$30) ^AB11</f>
-        <v>660425.24874536425</v>
+        <v>705829.06756064855</v>
       </c>
       <c r="AC13">
         <f>AC12 / (1+'Cost Components'!$B$30) ^AC11</f>
-        <v>617219.85864052724</v>
+        <v>659653.33416883019</v>
       </c>
       <c r="AD13">
         <f>AD12 / (1+'Cost Components'!$B$30) ^AD11</f>
-        <v>576840.98938367038</v>
+        <v>616498.44314843963</v>
       </c>
       <c r="AE13">
         <f>AE12 / (1+'Cost Components'!$B$30) ^AE11</f>
-        <v>539103.72839595366</v>
+        <v>576166.76929760713</v>
       </c>
       <c r="AF13">
         <f>AF12 / (1+'Cost Components'!$B$30) ^AF11</f>
-        <v>503835.26018313429</v>
+        <v>538473.61616598791</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="B17">
         <f>SUM(B13:AF13) /SUM(B15:AF15)</f>
-        <v>2.0270625378636451</v>
+        <v>2.1423223021110553</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -9089,123 +9089,123 @@
       </c>
       <c r="C22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!C20</f>
-        <v>7346938.3177570086</v>
+        <v>7856983.1775700934</v>
       </c>
       <c r="D22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!D20</f>
-        <v>6866297.4932308495</v>
+        <v>7342974.9323084988</v>
       </c>
       <c r="E22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!E20</f>
-        <v>6417100.4609634103</v>
+        <v>6862593.394680839</v>
       </c>
       <c r="F22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!F20</f>
-        <v>5997290.1504330942</v>
+        <v>6413638.6866176073</v>
       </c>
       <c r="G22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!G20</f>
-        <v>5604944.0658253217</v>
+        <v>5994054.8473061742</v>
       </c>
       <c r="H22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!H20</f>
-        <v>5238265.4820797397</v>
+        <v>5601920.4180431543</v>
       </c>
       <c r="I22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!I20</f>
-        <v>4895575.2168969531</v>
+        <v>5235439.6430309843</v>
       </c>
       <c r="J22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!J20</f>
-        <v>4575303.9410251901</v>
+        <v>4892934.2458233507</v>
       </c>
       <c r="K22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!K20</f>
-        <v>4275984.9916123264</v>
+        <v>4572835.7437601397</v>
       </c>
       <c r="L22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!L20</f>
-        <v>3996247.6557124546</v>
+        <v>4273678.2651963923</v>
       </c>
       <c r="M22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!M20</f>
-        <v>3734810.8931892095</v>
+        <v>3994091.8366321423</v>
       </c>
       <c r="N22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!N20</f>
-        <v>3490477.47027029</v>
+        <v>3732796.109002003</v>
       </c>
       <c r="O22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!O20</f>
-        <v>3262128.4768881211</v>
+        <v>3488594.494394395</v>
       </c>
       <c r="P22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!P20</f>
-        <v>3048718.2026991788</v>
+        <v>3260368.6863499018</v>
       </c>
       <c r="Q22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Q20</f>
-        <v>2849269.3483169894</v>
+        <v>3047073.5386447678</v>
       </c>
       <c r="R22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!R20</f>
-        <v>2662868.5498289624</v>
+        <v>2847732.2791072601</v>
       </c>
       <c r="S22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!S20</f>
-        <v>2488662.1961018341</v>
+        <v>2661432.0365488413</v>
       </c>
       <c r="T22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!T20</f>
-        <v>2325852.5197213399</v>
+        <v>2487319.6603260199</v>
       </c>
       <c r="U22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!U20</f>
-        <v>2173693.9436648036</v>
+        <v>2324597.8133888035</v>
       </c>
       <c r="V22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!V20</f>
-        <v>2031489.6669764521</v>
+        <v>2172521.3209241154</v>
       </c>
       <c r="W22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!W20</f>
-        <v>1898588.4738097682</v>
+        <v>2030393.757873005</v>
       </c>
       <c r="X22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!X20</f>
-        <v>1774381.7512240824</v>
+        <v>1897564.2596943972</v>
       </c>
       <c r="Y22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Y20</f>
-        <v>1658300.7020785818</v>
+        <v>1773424.5417704645</v>
       </c>
       <c r="Z22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Z20</f>
-        <v>1549813.7402603568</v>
+        <v>1657406.1138041725</v>
       </c>
       <c r="AA22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AA20</f>
-        <v>1448424.0563180903</v>
+        <v>1548977.6764524975</v>
       </c>
       <c r="AB22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AB20</f>
-        <v>1353667.3423533556</v>
+        <v>1447642.6882733623</v>
       </c>
       <c r="AC22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AC20</f>
-        <v>1265109.6657507992</v>
+        <v>1352937.0918442635</v>
       </c>
       <c r="AD22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AD20</f>
-        <v>1182345.4820100931</v>
+        <v>1264427.1886394988</v>
       </c>
       <c r="AE22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AE20</f>
-        <v>1104995.7775795262</v>
+        <v>1181707.652934111</v>
       </c>
       <c r="AF22" s="15">
         <f>('Cost Components'!$B$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AF20</f>
-        <v>1032706.334186473</v>
+        <v>1104399.6756393563</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -9445,123 +9445,123 @@
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
-        <v>11759755.286214951</v>
+        <v>12269800.146028038</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>11018899.595761638</v>
+        <v>11495577.034839287</v>
       </c>
       <c r="E25">
         <f t="shared" si="0"/>
-        <v>10326511.100010876</v>
+        <v>10772004.033728305</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>9679419.0479073618</v>
+        <v>10095767.584091876</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>9074660.1207078137</v>
+        <v>9463770.9021886662</v>
       </c>
       <c r="H25">
         <f t="shared" si="0"/>
-        <v>8509464.861642817</v>
+        <v>8873119.7976062316</v>
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
-        <v>7981244.9933577729</v>
+        <v>8321109.4194918042</v>
       </c>
       <c r="J25">
         <f t="shared" si="0"/>
-        <v>7487581.5650539938</v>
+        <v>7805211.8698521545</v>
       </c>
       <c r="K25">
         <f t="shared" si="0"/>
-        <v>7026213.8750504609</v>
+        <v>7323064.6271982733</v>
       </c>
       <c r="L25">
         <f t="shared" si="0"/>
-        <v>6595029.1180378133</v>
+        <v>6872459.7275217511</v>
       </c>
       <c r="M25">
         <f t="shared" si="0"/>
-        <v>6192052.7096147779</v>
+        <v>6451333.6530577112</v>
       </c>
       <c r="N25">
         <f t="shared" si="0"/>
-        <v>5815439.2437988594</v>
+        <v>6057757.8825305719</v>
       </c>
       <c r="O25">
         <f t="shared" si="0"/>
-        <v>5463464.0421017371</v>
+        <v>5689930.0596080106</v>
       </c>
       <c r="P25">
         <f t="shared" si="0"/>
-        <v>5134515.2554689134</v>
+        <v>5346165.7391196368</v>
       </c>
       <c r="Q25">
         <f t="shared" si="0"/>
-        <v>4827086.4829148725</v>
+        <v>5024890.6732426509</v>
       </c>
       <c r="R25">
         <f t="shared" si="0"/>
-        <v>4539769.8730512829</v>
+        <v>4724633.6023295801</v>
       </c>
       <c r="S25">
         <f t="shared" si="0"/>
-        <v>4271249.6769170873</v>
+        <v>4444019.517364094</v>
       </c>
       <c r="T25">
         <f t="shared" si="0"/>
-        <v>4020296.2225860623</v>
+        <v>4181763.3631907422</v>
       </c>
       <c r="U25">
         <f t="shared" si="0"/>
-        <v>3785760.2839589366</v>
+        <v>3936664.1536829364</v>
       </c>
       <c r="V25">
         <f t="shared" si="0"/>
-        <v>3566567.8179522771</v>
+        <v>3707599.4718999406</v>
       </c>
       <c r="W25">
         <f t="shared" si="0"/>
-        <v>3361715.0459834365</v>
+        <v>3493520.3300466733</v>
       </c>
       <c r="X25">
         <f t="shared" si="0"/>
-        <v>3170263.8572275108</v>
+        <v>3293446.3656978253</v>
       </c>
       <c r="Y25">
         <f t="shared" si="0"/>
-        <v>2991337.5125958044</v>
+        <v>3106461.3522876874</v>
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
-        <v>2824116.6297624339</v>
+        <v>2931709.0033062496</v>
       </c>
       <c r="AA25">
         <f t="shared" si="0"/>
-        <v>2667835.4308527419</v>
+        <v>2768389.0509871491</v>
       </c>
       <c r="AB25">
         <f t="shared" si="0"/>
-        <v>2521778.2356100394</v>
+        <v>2615753.5815300462</v>
       </c>
       <c r="AC25">
         <f t="shared" si="0"/>
-        <v>2385276.1839813446</v>
+        <v>2473103.6100748088</v>
       </c>
       <c r="AD25">
         <f t="shared" si="0"/>
-        <v>2257704.1731134066</v>
+        <v>2339785.8797428124</v>
       </c>
       <c r="AE25">
         <f t="shared" si="0"/>
-        <v>2138477.9947321559</v>
+        <v>2215189.8700867407</v>
       </c>
       <c r="AF25">
         <f t="shared" si="0"/>
-        <v>2027051.6597964072</v>
+        <v>2098745.0012492905</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B28" s="7">
         <f>SUM(B21:AF21) / SUM(B25:AF25)</f>
-        <v>0.28040033702919182</v>
+        <v>0.27066824143591162</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="B29" s="7">
         <f>SUM(B22:AF22) / SUM(B25:AF25)</f>
-        <v>0.517925248839749</v>
+        <v>0.53465703172954604</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="B30" s="7">
         <f>SUM(B23:AF23) / SUM(B25:AF25)</f>
-        <v>0.13234850038900139</v>
+        <v>0.12775496718907892</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B31" s="7">
         <f>SUM(B24:AF24) / SUM(B25:AF25)</f>
-        <v>6.9325913742057751E-2</v>
+        <v>6.691975964546347E-2</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
@@ -9846,123 +9846,123 @@
       </c>
       <c r="C36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!C34</f>
-        <v>2750803.7383177569</v>
+        <v>2997229.9065420558</v>
       </c>
       <c r="D36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!D34</f>
-        <v>2570844.6152502401</v>
+        <v>2801149.4453664073</v>
       </c>
       <c r="E36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!E34</f>
-        <v>2402658.5189254577</v>
+        <v>2617896.67791253</v>
       </c>
       <c r="F36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!F34</f>
-        <v>2245475.2513322039</v>
+        <v>2446632.4092640472</v>
       </c>
       <c r="G36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!G34</f>
-        <v>2098575.0012450502</v>
+        <v>2286572.3451065859</v>
       </c>
       <c r="H36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!H34</f>
-        <v>1961285.0478925703</v>
+        <v>2136983.5000996129</v>
       </c>
       <c r="I36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!I34</f>
-        <v>1832976.6802734302</v>
+        <v>1997180.8412145916</v>
       </c>
       <c r="J36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!J34</f>
-        <v>1713062.3180125516</v>
+        <v>1866524.1506678427</v>
       </c>
       <c r="K36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!K34</f>
-        <v>1600992.820572478</v>
+        <v>1744415.0940820957</v>
       </c>
       <c r="L36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!L34</f>
-        <v>1496254.972497643</v>
+        <v>1630294.4804505568</v>
       </c>
       <c r="M36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!M34</f>
-        <v>1398369.133175367</v>
+        <v>1523639.7013556603</v>
       </c>
       <c r="N36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!N34</f>
-        <v>1306887.0403508106</v>
+        <v>1423962.3377155708</v>
       </c>
       <c r="O36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!O34</f>
-        <v>1221389.757337206</v>
+        <v>1330805.923098664</v>
       </c>
       <c r="P36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!P34</f>
-        <v>1141485.7545207534</v>
+        <v>1243743.8533632376</v>
       </c>
       <c r="Q36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Q34</f>
-        <v>1066809.1163745357</v>
+        <v>1162377.4330497545</v>
       </c>
       <c r="R36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!R34</f>
-        <v>997017.86577059433</v>
+        <v>1086334.0495792101</v>
       </c>
       <c r="S36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!S34</f>
-        <v>931792.3979164433</v>
+        <v>1015265.4668964579</v>
       </c>
       <c r="T36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!T34</f>
-        <v>870834.01674433949</v>
+        <v>948846.23074435326</v>
       </c>
       <c r="U36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!U34</f>
-        <v>813863.56705078448</v>
+        <v>886772.17826575064</v>
       </c>
       <c r="V36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!V34</f>
-        <v>760620.1561222286</v>
+        <v>828759.04510817816</v>
       </c>
       <c r="W36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!W34</f>
-        <v>710859.958992737</v>
+        <v>774541.16365250293</v>
       </c>
       <c r="X36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!X34</f>
-        <v>664355.10186237097</v>
+        <v>723870.24640420836</v>
       </c>
       <c r="Y36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Y34</f>
-        <v>620892.61856296356</v>
+        <v>676514.24897589569</v>
       </c>
       <c r="Z36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Z34</f>
-        <v>580273.47529248928</v>
+        <v>632256.30745410803</v>
       </c>
       <c r="AA36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AA34</f>
-        <v>542311.65915185912</v>
+        <v>590893.7452842131</v>
       </c>
       <c r="AB36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AB34</f>
-        <v>506833.3263101487</v>
+        <v>552237.14512543287</v>
       </c>
       <c r="AC36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AC34</f>
-        <v>473676.00589733513</v>
+        <v>516109.48142563808</v>
       </c>
       <c r="AD36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AD34</f>
-        <v>442687.85597881797</v>
+        <v>482345.3097435871</v>
       </c>
       <c r="AE36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AE34</f>
-        <v>413726.96820450277</v>
+        <v>450790.00910615613</v>
       </c>
       <c r="AF36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AF34</f>
-        <v>386660.71794813348</v>
+        <v>421299.0739309871</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
@@ -10202,123 +10202,123 @@
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>3594911.0981308408</v>
+        <v>3841337.2663551401</v>
       </c>
       <c r="D39">
         <f t="shared" si="1"/>
-        <v>3370227.5449820943</v>
+        <v>3600532.3750982615</v>
       </c>
       <c r="E39">
         <f t="shared" si="1"/>
-        <v>3160242.9158711159</v>
+        <v>3375481.0748581882</v>
       </c>
       <c r="F39">
         <f t="shared" si="1"/>
-        <v>2963995.5989449685</v>
+        <v>3165152.7568768119</v>
       </c>
       <c r="G39">
         <f t="shared" si="1"/>
-        <v>2780586.8915373534</v>
+        <v>2968584.2353988895</v>
       </c>
       <c r="H39">
         <f t="shared" si="1"/>
-        <v>2609176.8846143493</v>
+        <v>2784875.3368213917</v>
       </c>
       <c r="I39">
         <f t="shared" si="1"/>
-        <v>2448980.6164620086</v>
+        <v>2613184.7774031702</v>
       </c>
       <c r="J39">
         <f t="shared" si="1"/>
-        <v>2299264.4780018772</v>
+        <v>2452726.3106571683</v>
       </c>
       <c r="K39">
         <f t="shared" si="1"/>
-        <v>2159342.8532727822</v>
+        <v>2302765.1267824001</v>
       </c>
       <c r="L39">
         <f t="shared" si="1"/>
-        <v>2028574.979694189</v>
+        <v>2162614.4876471027</v>
       </c>
       <c r="M39">
         <f t="shared" si="1"/>
-        <v>1906362.0137328866</v>
+        <v>2031632.58191318</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>1792144.2885354084</v>
+        <v>1909219.5859001686</v>
       </c>
       <c r="O39">
         <f t="shared" si="1"/>
-        <v>1685398.7509676712</v>
+        <v>1794814.9167291294</v>
       </c>
       <c r="P39">
         <f t="shared" si="1"/>
-        <v>1585636.5663249264</v>
+        <v>1687894.6651674109</v>
       </c>
       <c r="Q39">
         <f t="shared" si="1"/>
-        <v>1492400.8797429218</v>
+        <v>1587969.1964181405</v>
       </c>
       <c r="R39">
         <f t="shared" si="1"/>
-        <v>1405264.7240588057</v>
+        <v>1494580.9078674214</v>
       </c>
       <c r="S39">
         <f t="shared" si="1"/>
-        <v>1323829.0645409399</v>
+        <v>1407302.1335209545</v>
       </c>
       <c r="T39">
         <f t="shared" si="1"/>
-        <v>1247720.9715335886</v>
+        <v>1325733.1855336025</v>
       </c>
       <c r="U39">
         <f t="shared" si="1"/>
-        <v>1176591.9126482136</v>
+        <v>1249500.5238631796</v>
       </c>
       <c r="V39">
         <f t="shared" si="1"/>
-        <v>1110116.1566805735</v>
+        <v>1178255.045666523</v>
       </c>
       <c r="W39">
         <f t="shared" si="1"/>
-        <v>1047989.2819444613</v>
+        <v>1111670.4866042272</v>
       </c>
       <c r="X39">
         <f t="shared" si="1"/>
-        <v>989926.78219108516</v>
+        <v>1049441.9267329227</v>
       </c>
       <c r="Y39">
         <f t="shared" si="1"/>
-        <v>935662.76372998627</v>
+        <v>991284.39414291829</v>
       </c>
       <c r="Z39">
         <f t="shared" si="1"/>
-        <v>884948.72778503387</v>
+        <v>936931.5599466525</v>
       </c>
       <c r="AA39">
         <f t="shared" si="1"/>
-        <v>837552.43250937737</v>
+        <v>886134.51864173135</v>
       </c>
       <c r="AB39">
         <f t="shared" si="1"/>
-        <v>793256.82944801624</v>
+        <v>838660.64826330042</v>
       </c>
       <c r="AC39">
         <f t="shared" si="1"/>
-        <v>751859.06957758509</v>
+        <v>794292.54510588804</v>
       </c>
       <c r="AD39">
         <f t="shared" si="1"/>
-        <v>713169.57437157503</v>
+        <v>752827.02813634416</v>
       </c>
       <c r="AE39">
         <f t="shared" si="1"/>
-        <v>677011.16763698601</v>
+        <v>714074.20853863936</v>
       </c>
       <c r="AF39">
         <f t="shared" si="1"/>
-        <v>643218.26414671587</v>
+        <v>677856.62012956955</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="B41" s="7">
         <f>SUM(B35:AF35) / SUM(B39:AF39)</f>
-        <v>0.15244818890655634</v>
+        <v>0.1445073137443435</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="B42" s="7">
         <f>SUM(B36:AF36) / SUM(B39:AF39)</f>
-        <v>0.6134106647983617</v>
+        <v>0.63354772035735396</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="B43" s="7">
         <f>SUM(B37:AF37) / SUM(B39:AF39)</f>
-        <v>0.1532940322322392</v>
+        <v>0.14530909792898825</v>
       </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="B44" s="7">
         <f>SUM(B38:AF38) / SUM(B39:AF39)</f>
-        <v>8.0847114062842576E-2</v>
+        <v>7.6635867969314167E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10555,123 +10555,123 @@
       </c>
       <c r="C7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="D7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="E7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="F7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="G7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="H7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="I7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="J7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="K7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="L7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="M7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="N7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="O7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="P7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="Q7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="R7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="S7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="T7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="U7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="V7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="W7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="X7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="Y7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="Z7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="AA7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="AB7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="AC7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="AD7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="AE7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
       <c r="AF7">
         <f>('Cost Components'!$B$37-'Cost Components'!$B$17-'Cost Components'!$B$18-'Cost Components'!$B$20) * 10^6</f>
-        <v>8396501.8750000019</v>
+        <v>8658161.8750000037</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -10684,123 +10684,123 @@
       </c>
       <c r="C8">
         <f>C7 / (1+'Cost Components'!$B$30) ^C6</f>
-        <v>7847198.014018693</v>
+        <v>8091740.0700934613</v>
       </c>
       <c r="D8">
         <f>D7 / (1+'Cost Components'!$B$30) ^D6</f>
-        <v>7333829.9196436387</v>
+        <v>7562373.897283609</v>
       </c>
       <c r="E8">
         <f>E7 / (1+'Cost Components'!$B$30) ^E6</f>
-        <v>6854046.6538725588</v>
+        <v>7067639.1563398205</v>
       </c>
       <c r="F8">
         <f>F7 / (1+'Cost Components'!$B$30) ^F6</f>
-        <v>6405651.0783855692</v>
+        <v>6605270.2395699266</v>
       </c>
       <c r="G8">
         <f>G7 / (1+'Cost Components'!$B$30) ^G6</f>
-        <v>5986589.7928837091</v>
+        <v>6173149.7566074068</v>
       </c>
       <c r="H8">
         <f>H7 / (1+'Cost Components'!$B$30) ^H6</f>
-        <v>5594943.7316670185</v>
+        <v>5769298.837950848</v>
       </c>
       <c r="I8">
         <f>I7 / (1+'Cost Components'!$B$30) ^I6</f>
-        <v>5228919.3753897361</v>
+        <v>5391868.0728512593</v>
       </c>
       <c r="J8">
         <f>J7 / (1+'Cost Components'!$B$30) ^J6</f>
-        <v>4886840.5377474176</v>
+        <v>5039129.0400479063</v>
       </c>
       <c r="K8">
         <f>K7 / (1+'Cost Components'!$B$30) ^K6</f>
-        <v>4567140.6894835671</v>
+        <v>4709466.3925681366</v>
       </c>
       <c r="L8">
         <f>L7 / (1+'Cost Components'!$B$30) ^L6</f>
-        <v>4268355.7845640816</v>
+        <v>4401370.4603440529</v>
       </c>
       <c r="M8">
         <f>M7 / (1+'Cost Components'!$B$30) ^M6</f>
-        <v>3989117.5556673654</v>
+        <v>4113430.3367701424</v>
       </c>
       <c r="N8">
         <f>N7 / (1+'Cost Components'!$B$30) ^N6</f>
-        <v>3728147.2482872582</v>
+        <v>3844327.4175421898</v>
       </c>
       <c r="O8">
         <f>O7 / (1+'Cost Components'!$B$30) ^O6</f>
-        <v>3484249.7647544467</v>
+        <v>3592829.3621889623</v>
       </c>
       <c r="P8">
         <f>P7 / (1+'Cost Components'!$B$30) ^P6</f>
-        <v>3256308.191359296</v>
+        <v>3357784.4506438901</v>
       </c>
       <c r="Q8">
         <f>Q7 / (1+'Cost Components'!$B$30) ^Q6</f>
-        <v>3043278.6835133606</v>
+        <v>3138116.3090129811</v>
       </c>
       <c r="R8">
         <f>R7 / (1+'Cost Components'!$B$30) ^R6</f>
-        <v>2844185.6855265056</v>
+        <v>2932818.9803859638</v>
       </c>
       <c r="S8">
         <f>S7 / (1+'Cost Components'!$B$30) ^S6</f>
-        <v>2658117.4631088837</v>
+        <v>2740952.3181177233</v>
       </c>
       <c r="T8">
         <f>T7 / (1+'Cost Components'!$B$30) ^T6</f>
-        <v>2484221.9281391436</v>
+        <v>2561637.6804838534</v>
       </c>
       <c r="U8">
         <f>U7 / (1+'Cost Components'!$B$30) ^U6</f>
-        <v>2321702.7365786387</v>
+        <v>2394053.9069942553</v>
       </c>
       <c r="V8">
         <f>V7 / (1+'Cost Components'!$B$30) ^V6</f>
-        <v>2169815.6416622791</v>
+        <v>2237433.5579385567</v>
       </c>
       <c r="W8">
         <f>W7 / (1+'Cost Components'!$B$30) ^W6</f>
-        <v>2027865.0856656814</v>
+        <v>2091059.3999425762</v>
       </c>
       <c r="X8">
         <f>X7 / (1+'Cost Components'!$B$30) ^X6</f>
-        <v>1895201.0146408239</v>
+        <v>1954261.12144166</v>
       </c>
       <c r="Y8">
         <f>Y7 / (1+'Cost Components'!$B$30) ^Y6</f>
-        <v>1771215.9015334803</v>
+        <v>1826412.2630295889</v>
       </c>
       <c r="Z8">
         <f>Z7 / (1+'Cost Components'!$B$30) ^Z6</f>
-        <v>1655341.9640499814</v>
+        <v>1706927.3486257838</v>
       </c>
       <c r="AA8">
         <f>AA7 / (1+'Cost Components'!$B$30) ^AA6</f>
-        <v>1547048.5645326928</v>
+        <v>1595259.2043231623</v>
       </c>
       <c r="AB8">
         <f>AB7 / (1+'Cost Components'!$B$30) ^AB6</f>
-        <v>1445839.7799370962</v>
+        <v>1490896.4526384696</v>
       </c>
       <c r="AC8">
         <f>AC7 / (1+'Cost Components'!$B$30) ^AC6</f>
-        <v>1351252.1307823327</v>
+        <v>1393361.1706901581</v>
       </c>
       <c r="AD8">
         <f>AD7 / (1+'Cost Components'!$B$30) ^AD6</f>
-        <v>1262852.4586750774</v>
+        <v>1302206.7015795873</v>
       </c>
       <c r="AE8">
         <f>AE7 / (1+'Cost Components'!$B$30) ^AE6</f>
-        <v>1180235.9426869883</v>
+        <v>1217015.6089528853</v>
       </c>
       <c r="AF8">
         <f>AF7 / (1+'Cost Components'!$B$30) ^AF6</f>
-        <v>1103024.2455018582</v>
+        <v>1137397.7653765285</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="B12">
         <f>SUM(B8:AF8) /SUM(B10:AF10)</f>
-        <v>9.848496505529857</v>
+        <v>10.106282178471034</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Seymour_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Seymour_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{5F741EB4-9B88-E34F-9972-0A7EC792996A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA0F82CB-902E-4345-AD0C-AF0BAD2420D8}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -824,7 +824,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1172,14 +1172,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1193,12 +1193,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1234,12 +1234,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
         <v>10</v>
       </c>
@@ -1269,12 +1269,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1355,12 +1355,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
@@ -1375,12 +1375,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1410,12 +1410,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1445,12 +1445,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1480,12 +1480,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -1515,12 +1515,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C33" s="4">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1558,24 +1558,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>2024</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>131</v>
       </c>
@@ -1678,14 +1678,14 @@
       </c>
       <c r="M3" s="8">
         <f>'MFSP CO2 Corrected'!B17</f>
-        <v>2.1119513050548209</v>
+        <v>2.0412428194012882</v>
       </c>
       <c r="N3" s="8">
         <f>'MFSP WACC Corrected'!B17</f>
-        <v>2.1423223021110553</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.0726303516358775</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>131</v>
       </c>
@@ -1728,14 +1728,14 @@
       </c>
       <c r="M4" s="8">
         <f>M3/Inputs!$C$6</f>
-        <v>2.346612561172023</v>
+        <v>2.2680475771125423</v>
       </c>
       <c r="N4" s="8">
         <f>N3/Inputs!$C$6</f>
-        <v>2.3803581134567282</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.3029226129287528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>133</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>134</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>8.7962962962962958</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>136</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>137</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>79.903703703703712</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>137</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>2771.8275200000007</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>139</v>
       </c>
@@ -2028,14 +2028,14 @@
       </c>
       <c r="M10" s="14">
         <f>((M4-M5) /M9 )* 10^6</f>
-        <v>233.28022992282828</v>
+        <v>204.93611994751473</v>
       </c>
       <c r="N10" s="14">
         <f>((N4-N5) /N9 )* 10^6</f>
-        <v>245.4547076063117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>217.51808457719355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
         <v>140</v>
       </c>
@@ -2047,7 +2047,7 @@
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>141</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>305.14000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>142</v>
       </c>
@@ -2108,10 +2108,10 @@
       </c>
       <c r="K15" s="20">
         <f>K14*10^-6*Inputs!$C$33</f>
-        <v>0.15958822</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.15165458000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>143</v>
       </c>
@@ -2130,10 +2130,10 @@
       </c>
       <c r="K16" s="20">
         <f>N4+K15</f>
-        <v>2.539946333456728</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.454577192928753</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>144</v>
       </c>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="K17" s="4">
         <f>(K16-K5) /K9 * 10^6</f>
-        <v>303.02979799288806</v>
+        <v>272.2309333766745</v>
       </c>
     </row>
   </sheetData>
@@ -2169,17 +2169,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -2261,12 +2261,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -2395,12 +2395,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -2538,12 +2538,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -2637,12 +2637,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>76</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -2705,21 +2705,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>79</v>
       </c>
@@ -2735,7 +2735,7 @@
       <c r="J1" s="25"/>
       <c r="K1" s="26"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>81</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="26"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>82</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>89</v>
       </c>
@@ -3001,8 +3001,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>90</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="J13" s="25"/>
       <c r="K13" s="26"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>82</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>92</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>94</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="28" t="s">
         <v>95</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="J24" s="29"/>
       <c r="K24" s="29"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>93</v>
       </c>
@@ -3351,7 +3351,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>97</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>98</v>
       </c>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="H28" s="12">
         <f>(Inputs!C33*'Study Parameters'!C20) / 10^6</f>
-        <v>3.207036</v>
+        <v>3.0476040000000002</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>91</v>
@@ -3403,7 +3403,7 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>99</v>
       </c>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H29" s="23">
         <f>H27-H19+H28</f>
-        <v>4.0989985000000004</v>
+        <v>3.9395665000000002</v>
       </c>
       <c r="I29" s="22" t="s">
         <v>91</v>
@@ -3429,7 +3429,7 @@
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>7</v>
       </c>
@@ -3449,7 +3449,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="28" t="s">
         <v>100</v>
       </c>
@@ -3458,7 +3458,7 @@
       <c r="D32" s="29"/>
       <c r="E32" s="29"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>82</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>93</v>
       </c>
@@ -3489,7 +3489,7 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>97</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>98</v>
       </c>
@@ -3517,7 +3517,7 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>99</v>
       </c>
@@ -3550,17 +3550,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF44"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>9285726.8750000019</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>2148507.7932526348</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>489840.17772722145</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -4183,12 +4183,12 @@
         <v>4.969113935214537</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>3382180.5</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>103</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>782560.29498359468</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>489840.17772722145</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>1.7976211653116483</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -4843,7 +4843,7 @@
       <c r="AE21" s="15"/>
       <c r="AF21" s="15"/>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
@@ -4875,10 +4875,10 @@
       <c r="AE22" s="15"/>
       <c r="AF22" s="15"/>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B23" s="15"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -4911,22 +4911,22 @@
       <c r="AE24" s="15"/>
       <c r="AF24" s="15"/>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B27" s="7"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B28" s="7"/>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B29" s="7"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B30" s="7"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
@@ -4958,7 +4958,7 @@
       <c r="AE35" s="15"/>
       <c r="AF35" s="15"/>
     </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
@@ -4990,10 +4990,10 @@
       <c r="AE36" s="15"/>
       <c r="AF36" s="15"/>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B37" s="15"/>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
@@ -5026,19 +5026,19 @@
       <c r="AE38" s="15"/>
       <c r="AF38" s="15"/>
     </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B40" s="7"/>
     </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B42" s="7"/>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B43" s="7"/>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B44" s="7"/>
     </row>
   </sheetData>
@@ -5049,14 +5049,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AF17"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>9535526.8750000019</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>2206305.8799268682</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>489840.17772722145</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -5679,12 +5679,12 @@
         <v>5.0709081677093488</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>2112230.5</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>103</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>488722.50406308757</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>489840.17772722145</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -6315,20 +6315,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AF17"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="32" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="32" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>13098218.875</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>3030632.4652335043</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>489840.17772722145</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -6951,12 +6951,12 @@
         <v>6.6509708850468314</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -7064,126 +7064,126 @@
       </c>
       <c r="C12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="D12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="E12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="F12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="G12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="H12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="I12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="J12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="K12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="L12">
         <f>'Cost Components'!$H$29 * 10^6 + 'Cost Components'!H10 * 10^6</f>
-        <v>5172998.5</v>
+        <v>5013566.5</v>
       </c>
       <c r="M12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="N12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="O12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="P12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="Q12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="R12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="S12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="T12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="U12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="V12">
         <f>'Cost Components'!$H$29 * 10^6+ 'Cost Components'!H10 * 10^6</f>
-        <v>5172998.5</v>
+        <v>5013566.5</v>
       </c>
       <c r="W12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="X12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="Y12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="Z12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AA12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AB12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AC12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AD12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AE12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AF12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+        <v>3939566.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>103</v>
       </c>
@@ -7193,126 +7193,126 @@
       </c>
       <c r="C13">
         <f>C12 / (1+'Study Parameters'!$C$3) ^C11</f>
-        <v>3903808.0952380956</v>
+        <v>3751968.0952380951</v>
       </c>
       <c r="D13">
         <f>D12 / (1+'Study Parameters'!$C$3) ^D11</f>
-        <v>3717912.4716553292</v>
+        <v>3573302.947845805</v>
       </c>
       <c r="E13">
         <f>E12 / (1+'Study Parameters'!$C$3) ^E11</f>
-        <v>3540869.0206241226</v>
+        <v>3403145.6646150518</v>
       </c>
       <c r="F13">
         <f>F12 / (1+'Study Parameters'!$C$3) ^F11</f>
-        <v>3372256.2101182123</v>
+        <v>3241091.1091571925</v>
       </c>
       <c r="G13">
         <f>G12 / (1+'Study Parameters'!$C$3) ^G11</f>
-        <v>3211672.5810649637</v>
+        <v>3086753.4372925642</v>
       </c>
       <c r="H13">
         <f>H12 / (1+'Study Parameters'!$C$3) ^H11</f>
-        <v>3058735.7914904421</v>
+        <v>2939765.1783738709</v>
       </c>
       <c r="I13">
         <f>I12 / (1+'Study Parameters'!$C$3) ^I11</f>
-        <v>2913081.706181373</v>
+        <v>2799776.3603560673</v>
       </c>
       <c r="J13">
         <f>J12 / (1+'Study Parameters'!$C$3) ^J11</f>
-        <v>2774363.529696546</v>
+        <v>2666453.6765295882</v>
       </c>
       <c r="K13">
         <f>K12 / (1+'Study Parameters'!$C$3) ^K11</f>
-        <v>2642250.9806633769</v>
+        <v>2539479.6919329409</v>
       </c>
       <c r="L13">
         <f>L12 / (1+'Study Parameters'!$C$3) ^L11</f>
-        <v>3175772.3396964674</v>
+        <v>3077894.9218579573</v>
       </c>
       <c r="M13">
         <f>M12 / (1+'Study Parameters'!$C$3) ^M11</f>
-        <v>2396599.5289463736</v>
+        <v>2303382.9405287444</v>
       </c>
       <c r="N13">
         <f>N12 / (1+'Study Parameters'!$C$3) ^N11</f>
-        <v>2282475.7418536893</v>
+        <v>2193698.0385988043</v>
       </c>
       <c r="O13">
         <f>O12 / (1+'Study Parameters'!$C$3) ^O11</f>
-        <v>2173786.4208130371</v>
+        <v>2089236.2272369564</v>
       </c>
       <c r="P13">
         <f>P12 / (1+'Study Parameters'!$C$3) ^P11</f>
-        <v>2070272.7817267026</v>
+        <v>1989748.7878447208</v>
       </c>
       <c r="Q13">
         <f>Q12 / (1+'Study Parameters'!$C$3) ^Q11</f>
-        <v>1971688.3635492399</v>
+        <v>1894998.8455664001</v>
       </c>
       <c r="R13">
         <f>R12 / (1+'Study Parameters'!$C$3) ^R11</f>
-        <v>1877798.4414754668</v>
+        <v>1804760.8053013335</v>
       </c>
       <c r="S13">
         <f>S12 / (1+'Study Parameters'!$C$3) ^S11</f>
-        <v>1788379.4680718728</v>
+        <v>1718819.8145726984</v>
       </c>
       <c r="T13">
         <f>T12 / (1+'Study Parameters'!$C$3) ^T11</f>
-        <v>1703218.5410208313</v>
+        <v>1636971.2519739985</v>
       </c>
       <c r="U13">
         <f>U12 / (1+'Study Parameters'!$C$3) ^U11</f>
-        <v>1622112.8962103154</v>
+        <v>1559020.2399752366</v>
       </c>
       <c r="V13">
         <f>V12 / (1+'Study Parameters'!$C$3) ^V11</f>
-        <v>1949648.7295678079</v>
+        <v>1889560.4855343995</v>
       </c>
       <c r="W13">
         <f>W12 / (1+'Study Parameters'!$C$3) ^W11</f>
-        <v>1471304.2142497194</v>
+        <v>1414077.3151702827</v>
       </c>
       <c r="X13">
         <f>X12 / (1+'Study Parameters'!$C$3) ^X11</f>
-        <v>1401242.1088092567</v>
+        <v>1346740.3001621743</v>
       </c>
       <c r="Y13">
         <f>Y12 / (1+'Study Parameters'!$C$3) ^Y11</f>
-        <v>1334516.2941040536</v>
+        <v>1282609.8096782609</v>
       </c>
       <c r="Z13">
         <f>Z12 / (1+'Study Parameters'!$C$3) ^Z11</f>
-        <v>1270967.899146718</v>
+        <v>1221533.1520745342</v>
       </c>
       <c r="AA13">
         <f>AA12 / (1+'Study Parameters'!$C$3) ^AA11</f>
-        <v>1210445.6182349694</v>
+        <v>1163364.9067376517</v>
       </c>
       <c r="AB13">
         <f>AB12 / (1+'Study Parameters'!$C$3) ^AB11</f>
-        <v>1152805.350699971</v>
+        <v>1107966.5778453825</v>
       </c>
       <c r="AC13">
         <f>AC12 / (1+'Study Parameters'!$C$3) ^AC11</f>
-        <v>1097909.8578094959</v>
+        <v>1055206.26461465</v>
       </c>
       <c r="AD13">
         <f>AD12 / (1+'Study Parameters'!$C$3) ^AD11</f>
-        <v>1045628.4360090439</v>
+        <v>1004958.3472520477</v>
       </c>
       <c r="AE13">
         <f>AE12 / (1+'Study Parameters'!$C$3) ^AE11</f>
-        <v>995836.60572289873</v>
+        <v>957103.18785909284</v>
       </c>
       <c r="AF13">
         <f>AF12 / (1+'Study Parameters'!$C$3) ^AF11</f>
-        <v>948415.81497418962</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+        <v>911526.84558008879</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -7570,13 +7570,13 @@
         <v>489840.17772722145</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>106</v>
       </c>
       <c r="B17">
         <f>SUM(B13:AF13) /SUM(B15:AF15)</f>
-        <v>2.1119513050548209</v>
+        <v>2.0412428194012882</v>
       </c>
     </row>
   </sheetData>
@@ -7587,18 +7587,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AF44"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="32" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>13098218.875</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>1720675.2534685845</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>278112.20319153508</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -8221,12 +8221,12 @@
         <v>6.719635538021123</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -8334,126 +8334,126 @@
       </c>
       <c r="C12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="D12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="E12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="F12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="G12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="H12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="I12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="J12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="K12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="L12">
         <f>'Cost Components'!$H$29 * 10^6 + 'Cost Components'!H10 * 10^6</f>
-        <v>5172998.5</v>
+        <v>5013566.5</v>
       </c>
       <c r="M12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="N12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="O12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="P12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="Q12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="R12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="S12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="T12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="U12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="V12">
         <f>'Cost Components'!$H$29 * 10^6+ 'Cost Components'!H10 * 10^6</f>
-        <v>5172998.5</v>
+        <v>5013566.5</v>
       </c>
       <c r="W12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="X12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="Y12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="Z12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AA12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AB12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AC12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AD12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AE12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
+        <v>3939566.5</v>
       </c>
       <c r="AF12">
         <f>'Cost Components'!$H$29 * 10^6</f>
-        <v>4098998.5000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+        <v>3939566.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>103</v>
       </c>
@@ -8463,126 +8463,126 @@
       </c>
       <c r="C13">
         <f>C12 / (1+'Cost Components'!$B$30) ^C11</f>
-        <v>3830839.7196261683</v>
+        <v>3681837.8504672893</v>
       </c>
       <c r="D13">
         <f>D12 / (1+'Cost Components'!$B$30) ^D11</f>
-        <v>3580224.0370338024</v>
+        <v>3440969.9537077472</v>
       </c>
       <c r="E13">
         <f>E12 / (1+'Cost Components'!$B$30) ^E11</f>
-        <v>3346003.7729287869</v>
+        <v>3215859.7698203246</v>
       </c>
       <c r="F13">
         <f>F12 / (1+'Cost Components'!$B$30) ^F11</f>
-        <v>3127106.3298399881</v>
+        <v>3005476.4203928267</v>
       </c>
       <c r="G13">
         <f>G12 / (1+'Cost Components'!$B$30) ^G11</f>
-        <v>2922529.2802242879</v>
+        <v>2808856.4676568471</v>
       </c>
       <c r="H13">
         <f>H12 / (1+'Cost Components'!$B$30) ^H11</f>
-        <v>2731335.7759105493</v>
+        <v>2625099.502483035</v>
       </c>
       <c r="I13">
         <f>I12 / (1+'Cost Components'!$B$30) ^I11</f>
-        <v>2552650.2578603262</v>
+        <v>2453364.0210121819</v>
       </c>
       <c r="J13">
         <f>J12 / (1+'Cost Components'!$B$30) ^J11</f>
-        <v>2385654.4465984358</v>
+        <v>2292863.5710394224</v>
       </c>
       <c r="K13">
         <f>K12 / (1+'Cost Components'!$B$30) ^K11</f>
-        <v>2229583.5949518089</v>
+        <v>2142863.1505041327</v>
       </c>
       <c r="L13">
         <f>L12 / (1+'Cost Components'!$B$30) ^L11</f>
-        <v>2629690.1256889571</v>
+        <v>2548642.9813453346</v>
       </c>
       <c r="M13">
         <f>M12 / (1+'Cost Components'!$B$30) ^M11</f>
-        <v>1947404.6597535233</v>
+        <v>1871659.6650398574</v>
       </c>
       <c r="N13">
         <f>N12 / (1+'Cost Components'!$B$30) ^N11</f>
-        <v>1820004.3549098354</v>
+        <v>1749214.6402241662</v>
       </c>
       <c r="O13">
         <f>O12 / (1+'Cost Components'!$B$30) ^O11</f>
-        <v>1700938.6494484441</v>
+        <v>1634780.0375926786</v>
       </c>
       <c r="P13">
         <f>P12 / (1+'Cost Components'!$B$30) ^P11</f>
-        <v>1589662.2892041535</v>
+        <v>1527831.8108342791</v>
       </c>
       <c r="Q13">
         <f>Q12 / (1+'Cost Components'!$B$30) ^Q11</f>
-        <v>1485665.6908450029</v>
+        <v>1427880.1970413821</v>
       </c>
       <c r="R13">
         <f>R12 / (1+'Cost Components'!$B$30) ^R11</f>
-        <v>1388472.608266358</v>
+        <v>1334467.4738704509</v>
       </c>
       <c r="S13">
         <f>S12 / (1+'Cost Components'!$B$30) ^S11</f>
-        <v>1297637.951650802</v>
+        <v>1247165.8634303277</v>
       </c>
       <c r="T13">
         <f>T12 / (1+'Cost Components'!$B$30) ^T11</f>
-        <v>1212745.7492063569</v>
+        <v>1165575.5732993719</v>
       </c>
       <c r="U13">
         <f>U12 / (1+'Cost Components'!$B$30) ^U11</f>
-        <v>1133407.2422489317</v>
+        <v>1089322.9657003474</v>
       </c>
       <c r="V13">
         <f>V12 / (1+'Cost Components'!$B$30) ^V11</f>
-        <v>1336801.1139276386</v>
+        <v>1295600.8554710178</v>
       </c>
       <c r="W13">
         <f>W12 / (1+'Cost Components'!$B$30) ^W11</f>
-        <v>989961.78028555482</v>
+        <v>951456.86584011477</v>
       </c>
       <c r="X13">
         <f>X12 / (1+'Cost Components'!$B$30) ^X11</f>
-        <v>925197.92550051853</v>
+        <v>889212.02414964</v>
       </c>
       <c r="Y13">
         <f>Y12 / (1+'Cost Components'!$B$30) ^Y11</f>
-        <v>864670.95841169951</v>
+        <v>831039.2749062056</v>
       </c>
       <c r="Z13">
         <f>Z12 / (1+'Cost Components'!$B$30) ^Z11</f>
-        <v>808103.69945018645</v>
+        <v>776672.21953850985</v>
       </c>
       <c r="AA13">
         <f>AA12 / (1+'Cost Components'!$B$30) ^AA11</f>
-        <v>755237.10228989378</v>
+        <v>725861.88741916802</v>
       </c>
       <c r="AB13">
         <f>AB12 / (1+'Cost Components'!$B$30) ^AB11</f>
-        <v>705829.06756064855</v>
+        <v>678375.59571884875</v>
       </c>
       <c r="AC13">
         <f>AC12 / (1+'Cost Components'!$B$30) ^AC11</f>
-        <v>659653.33416883019</v>
+        <v>633995.88384939113</v>
       </c>
       <c r="AD13">
         <f>AD12 / (1+'Cost Components'!$B$30) ^AD11</f>
-        <v>616498.44314843963</v>
+        <v>592519.51761625358</v>
       </c>
       <c r="AE13">
         <f>AE12 / (1+'Cost Components'!$B$30) ^AE11</f>
-        <v>576166.76929760713</v>
+        <v>553756.55851986306</v>
       </c>
       <c r="AF13">
         <f>AF12 / (1+'Cost Components'!$B$30) ^AF11</f>
-        <v>538473.61616598791</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+        <v>517529.49394379731</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -8711,7 +8711,7 @@
         <v>2117061.0211706101</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -8840,21 +8840,21 @@
         <v>278112.20319153508</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>106</v>
       </c>
       <c r="B17">
         <f>SUM(B13:AF13) /SUM(B15:AF15)</f>
-        <v>2.1423223021110553</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+        <v>2.0726303516358775</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>109</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>559098.45060993417</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>110</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>1104399.6756393563</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>111</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>435246.875</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -9564,13 +9564,13 @@
         <v>2098745.0012492905</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27" s="7"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>93</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>0.27066824143591162</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>115</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>0.53465703172954604</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>0.12775496718907892</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>116</v>
       </c>
@@ -9606,12 +9606,12 @@
         <v>6.691975964546347E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>109</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>96095.046198582437</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -9846,126 +9846,126 @@
       </c>
       <c r="C36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!C34</f>
-        <v>2997229.9065420558</v>
+        <v>2848228.0373831773</v>
       </c>
       <c r="D36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!D34</f>
-        <v>2801149.4453664073</v>
+        <v>2661895.362040353</v>
       </c>
       <c r="E36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!E34</f>
-        <v>2617896.67791253</v>
+        <v>2487752.6748040677</v>
       </c>
       <c r="F36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!F34</f>
-        <v>2446632.4092640472</v>
+        <v>2325002.4998168861</v>
       </c>
       <c r="G36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!G34</f>
-        <v>2286572.3451065859</v>
+        <v>2172899.5325391456</v>
       </c>
       <c r="H36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!H34</f>
-        <v>2136983.5000996129</v>
+        <v>2030747.226672099</v>
       </c>
       <c r="I36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!I34</f>
-        <v>1997180.8412145916</v>
+        <v>1897894.6043664473</v>
       </c>
       <c r="J36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!J34</f>
-        <v>1866524.1506678427</v>
+        <v>1773733.2751088294</v>
       </c>
       <c r="K36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!K34</f>
-        <v>1744415.0940820957</v>
+        <v>1657694.6496344197</v>
       </c>
       <c r="L36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!L34</f>
-        <v>1630294.4804505568</v>
+        <v>1549247.3361069346</v>
       </c>
       <c r="M36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!M34</f>
-        <v>1523639.7013556603</v>
+        <v>1447894.7066419946</v>
       </c>
       <c r="N36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!N34</f>
-        <v>1423962.3377155708</v>
+        <v>1353172.6230299019</v>
       </c>
       <c r="O36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!O34</f>
-        <v>1330805.923098664</v>
+        <v>1264647.3112428987</v>
       </c>
       <c r="P36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!P34</f>
-        <v>1243743.8533632376</v>
+        <v>1181913.3749933634</v>
       </c>
       <c r="Q36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Q34</f>
-        <v>1162377.4330497545</v>
+        <v>1104591.9392461339</v>
       </c>
       <c r="R36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!R34</f>
-        <v>1086334.0495792101</v>
+        <v>1032328.9151833028</v>
       </c>
       <c r="S36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!S34</f>
-        <v>1015265.4668964579</v>
+        <v>964793.37867598399</v>
       </c>
       <c r="T36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!T34</f>
-        <v>948846.23074435326</v>
+        <v>901676.0548373682</v>
       </c>
       <c r="U36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!U34</f>
-        <v>886772.17826575064</v>
+        <v>842687.90171716642</v>
       </c>
       <c r="V36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!V34</f>
-        <v>828759.04510817816</v>
+        <v>787558.78665155754</v>
       </c>
       <c r="W36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!W34</f>
-        <v>774541.16365250293</v>
+        <v>736036.249207063</v>
       </c>
       <c r="X36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!X34</f>
-        <v>723870.24640420836</v>
+        <v>687884.34505332995</v>
       </c>
       <c r="Y36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Y34</f>
-        <v>676514.24897589569</v>
+        <v>642882.56547040178</v>
       </c>
       <c r="Z36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!Z34</f>
-        <v>632256.30745410803</v>
+        <v>600824.82754243154</v>
       </c>
       <c r="AA36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AA34</f>
-        <v>590893.7452842131</v>
+        <v>561518.53041348746</v>
       </c>
       <c r="AB36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AB34</f>
-        <v>552237.14512543287</v>
+        <v>524783.67328363319</v>
       </c>
       <c r="AC36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AC34</f>
-        <v>516109.48142563808</v>
+        <v>490452.03110619908</v>
       </c>
       <c r="AD36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AD34</f>
-        <v>482345.3097435871</v>
+        <v>458366.38421140111</v>
       </c>
       <c r="AE36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AE34</f>
-        <v>450790.00910615613</v>
+        <v>428379.79832841223</v>
       </c>
       <c r="AF36" s="15">
         <f>('Cost Components'!$H$28 * 10^6) / (1+Inputs!$C$5) ^'MFSP WACC Corrected'!AF34</f>
-        <v>421299.0739309871</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+        <v>400354.95170879649</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>160462.49999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -10202,165 +10202,165 @@
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>3841337.2663551401</v>
+        <v>3692335.3971962612</v>
       </c>
       <c r="D39">
         <f t="shared" si="1"/>
-        <v>3600532.3750982615</v>
+        <v>3461278.2917722072</v>
       </c>
       <c r="E39">
         <f t="shared" si="1"/>
-        <v>3375481.0748581882</v>
+        <v>3245337.0717497258</v>
       </c>
       <c r="F39">
         <f t="shared" si="1"/>
-        <v>3165152.7568768119</v>
+        <v>3043522.8474296508</v>
       </c>
       <c r="G39">
         <f t="shared" si="1"/>
-        <v>2968584.2353988895</v>
+        <v>2854911.4228314487</v>
       </c>
       <c r="H39">
         <f t="shared" si="1"/>
-        <v>2784875.3368213917</v>
+        <v>2678639.0633938778</v>
       </c>
       <c r="I39">
         <f t="shared" si="1"/>
-        <v>2613184.7774031702</v>
+        <v>2513898.5405550255</v>
       </c>
       <c r="J39">
         <f t="shared" si="1"/>
-        <v>2452726.3106571683</v>
+        <v>2359935.4350981549</v>
       </c>
       <c r="K39">
         <f t="shared" si="1"/>
-        <v>2302765.1267824001</v>
+        <v>2216044.6823347239</v>
       </c>
       <c r="L39">
         <f t="shared" si="1"/>
-        <v>2162614.4876471027</v>
+        <v>2081567.3433034807</v>
       </c>
       <c r="M39">
         <f t="shared" si="1"/>
-        <v>2031632.58191318</v>
+        <v>1955887.5871995143</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>1909219.5859001686</v>
+        <v>1838429.8712144997</v>
       </c>
       <c r="O39">
         <f t="shared" si="1"/>
-        <v>1794814.9167291294</v>
+        <v>1728656.304873364</v>
       </c>
       <c r="P39">
         <f t="shared" si="1"/>
-        <v>1687894.6651674109</v>
+        <v>1626064.1867975364</v>
       </c>
       <c r="Q39">
         <f t="shared" si="1"/>
-        <v>1587969.1964181405</v>
+        <v>1530183.70261452</v>
       </c>
       <c r="R39">
         <f t="shared" si="1"/>
-        <v>1494580.9078674214</v>
+        <v>1440575.7734715142</v>
       </c>
       <c r="S39">
         <f t="shared" si="1"/>
-        <v>1407302.1335209545</v>
+        <v>1356830.0453004804</v>
       </c>
       <c r="T39">
         <f t="shared" si="1"/>
-        <v>1325733.1855336025</v>
+        <v>1278563.0096266174</v>
       </c>
       <c r="U39">
         <f t="shared" si="1"/>
-        <v>1249500.5238631796</v>
+        <v>1205416.2473145954</v>
       </c>
       <c r="V39">
         <f t="shared" si="1"/>
-        <v>1178255.045666523</v>
+        <v>1137054.7872099024</v>
       </c>
       <c r="W39">
         <f t="shared" si="1"/>
-        <v>1111670.4866042272</v>
+        <v>1073165.5721587872</v>
       </c>
       <c r="X39">
         <f t="shared" si="1"/>
-        <v>1049441.9267329227</v>
+        <v>1013456.0253820443</v>
       </c>
       <c r="Y39">
         <f t="shared" si="1"/>
-        <v>991284.39414291829</v>
+        <v>957652.71063742437</v>
       </c>
       <c r="Z39">
         <f t="shared" si="1"/>
-        <v>936931.5599466525</v>
+        <v>905500.08003497613</v>
       </c>
       <c r="AA39">
         <f t="shared" si="1"/>
-        <v>886134.51864173135</v>
+        <v>856759.30377100571</v>
       </c>
       <c r="AB39">
         <f t="shared" si="1"/>
-        <v>838660.64826330042</v>
+        <v>811207.17642150074</v>
       </c>
       <c r="AC39">
         <f t="shared" si="1"/>
-        <v>794292.54510588804</v>
+        <v>768635.0947864491</v>
       </c>
       <c r="AD39">
         <f t="shared" si="1"/>
-        <v>752827.02813634416</v>
+        <v>728848.10260415811</v>
       </c>
       <c r="AE39">
         <f t="shared" si="1"/>
-        <v>714074.20853863936</v>
+        <v>691663.99776089541</v>
       </c>
       <c r="AF39">
         <f t="shared" si="1"/>
-        <v>677856.62012956955</v>
-      </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+        <v>656912.49790737894</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>118</v>
       </c>
       <c r="B40" s="7"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>93</v>
       </c>
       <c r="B41" s="7">
         <f>SUM(B35:AF35) / SUM(B39:AF39)</f>
-        <v>0.1445073137443435</v>
-      </c>
-    </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0.14920667960450337</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>115</v>
       </c>
       <c r="B42" s="7">
         <f>SUM(B36:AF36) / SUM(B39:AF39)</f>
-        <v>0.63354772035735396</v>
-      </c>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0.62163072261025676</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>81</v>
       </c>
       <c r="B43" s="7">
         <f>SUM(B37:AF37) / SUM(B39:AF39)</f>
-        <v>0.14530909792898825</v>
-      </c>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0.15003453774434736</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>116</v>
       </c>
       <c r="B44" s="7">
         <f>SUM(B38:AF38) / SUM(B39:AF39)</f>
-        <v>7.6635867969314167E-2</v>
+        <v>7.9128060040892345E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10371,12 +10371,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="89.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>119</v>
       </c>
@@ -10389,13 +10389,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AF12"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>122</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -10442,12 +10442,12 @@
         <v>1015029.2567256349</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>8658161.8750000037</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>1137397.7653765285</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>1015029.2567256349</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>133341.4672836127</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>106</v>
       </c>
